--- a/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
+++ b/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
@@ -12,17 +12,19 @@
     <sheet name="SQL" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="JavaScript" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Creatio_BPMSoft" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Резюме_и_поведение" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Как_готовиться" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SQL_шпаргалка" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Архитектура_очереди" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Резюме_и_поведение" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Как_готовиться" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SQL_шпаргалка" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C#'!$A$1:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SQL'!$A$1:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'JavaScript'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Creatio_BPMSoft'!$A$1:$D$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Резюме_и_поведение'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Как_готовиться'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Архитектура_очереди'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Резюме_и_поведение'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Как_готовиться'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -594,76 +596,96 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Резюме_и_поведение</t>
+          <t>Архитектура_очереди</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Разговорная часть</t>
+          <t>IIS, Redis, БД, Rabbit, Kafka</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ЗАРАНЕЕ впишите факты из резюме</t>
+          <t>Схема стенда + сравнение очередей</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Резюме_и_поведение</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Разговорная часть</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ЗАРАНЕЕ впишите факты из резюме</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Как_готовиться</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>План на дни</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Идите сверху вниз, отмечайте статус</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Кандидат</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Владислав Пыжьянов</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Стиль файла</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Ответы написаны простым языком «для чайников»: аналогии, шаги, и блок «Что сказать» — готовая короткая формулировка на собеседование.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="50" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Стиль файла</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ответы написаны простым языком «для чайников»: аналогии, шаги, и блок «Что сказать» — готовая короткая формулировка на собеседование.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Совет</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Не зубрите наизусть длинный текст. Понимайте аналогию → своими словами скажите короткий ответ из блока «Что сказать» → один пример из вашего опыта.</t>
         </is>
@@ -2708,6 +2730,510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Ответ простыми словами</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Статус (ок/повторить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="220" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Общая картина</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Из чего состоит типичное приложение Creatio / веб на .NET?</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Представьте ресторан:
+• официант принимает заказ (веб-сервер / IIS / reverse proxy);
+• кухня готовит (приложение Creatio / .NET);
+• холодильник с продуктами (база данных);
+• записка «уже готовили вот это» на стикере (кэш Redis);
+• лента заказов между цехами (очередь Rabbit/Kafka — если есть интеграции).
+Типичный набор для Creatio on-prem / корпоративного стенда:
+1) Браузер пользователя
+2) IIS (или другой web-сервер) — принимает HTTP
+3) Приложение Creatio (.NET) — бизнес-логика, процессы, API
+4) СУБД (MS SQL / PostgreSQL) — главное хранилище
+5) Redis — быстрый кэш и иногда сессии/распределённые штуки
+6) Файловое хранилище (диск / S3-подобное) — вложения
+7) Опционально: планировщик, Elasticsearch, очереди, почтовый сервер
+Что сказать: «Клиент → IIS/web → приложение → БД; рядом Redis-кэш; для интеграций часто очереди; вложения отдельно».</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="220" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>IIS</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Что такое IIS и зачем он нужен?</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>IIS (Internet Information Services) — веб-сервер Windows от Microsoft.
+Простыми словами: это «дверь в интернет» для сайта/приложения. Браузер стучится на порт 80/443, IIS принимает запрос и отдаёт его приложению Creatio (или статику), потом возвращает ответ.
+Что обычно настраивают:
+• сайт / application pool (пул — «рабочий процесс» приложения);
+• HTTPS-сертификат;
+• привязку к домену;
+• права учётки пула на папки и БД.
+Аналогия: ресепшен офиса — посетитель не бежит сразу в бухгалтерию, сначала проходит через ресепшен.
+Что сказать: «IIS хостит веб-приложение Creatio, раздаёт HTTP/HTTPS, управляет app pool».</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="194" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>IIS</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Что такое Application Pool?</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Пул приложений — отдельный рабочий процесс Windows, в котором крутится сайт.
+Зачем отдельно: упал один сайт — не обязательно уронил все остальные; можно задать свою учётку, лимиты памяти, автоперезапуск.
+Если пул «засыпает» или часто перезапускается — пользователи видят долгий первый заход или обрыв сессий.
+Что сказать: «Изолированный worker process для сайта; влияет на стабильность и права».</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="220" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Какая роль базы данных?</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>БД — главный сейф с данными: контакты, сделки, настройки, права, журналы.
+Creatio без БД не живёт. Всё важное в итоге там (или согласовано с ней).
+Рядом бывают:
+• основная OLTP-база (повседневная работа);
+• иногда реплика/отчётная база для тяжёлых отчётов;
+• бэкапы.
+Что сказать: «СУБД — источник истины; кэш ускоряет чтение, но не заменяет БД».</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Redis</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Что такое Redis простыми словами?</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Redis — очень быстрое хранилище «ключ → значение» обычно в памяти (RAM).
+Аналогия: не ходить каждый раз в большой архив (БД), а держать частые бумажки на столе под рукой.
+Зачем в приложениях / Creatio-ландшафте:
+• кэш справочников и тяжёлых выборок;
+• сессии / распределённый кэш между несколькими серверами;
+• иногда блокировки, счётчики, pub/sub.
+Важно: данные в Redis могут пропасть при рестарте (зависит от настроек). Туда не кладут единственную копию критичных денег/сделок — только то, что можно заново прочитать из БД.
+Что сказать: «In-memory кэш/ключ-значение; ускоряет чтение; источник истины — БД».</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="220" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Redis</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Как примерно работают с Redis из кода?</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Идея:
+1) Спросили: есть ли в кэше ключ user:123:profile?
+2) Есть — вернули быстро.
+3) Нет — прочитали из БД, положили в Redis с TTL (время жизни), вернули.
+В .NET часто используют StackExchange.Redis: Multiplexer → Database → StringGet/StringSet.
+Правила чайника:
+• ключи именуйте системно (префикс:сущность:id);
+• всегда думайте про TTL и инвалидацию (когда данные в БД изменились — сбросить кэш);
+• не храните огромные объекты без нужды.
+Что сказать: «Cache-aside: сначала Redis, промах → БД → запись в Redis с TTL».</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="220" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Другие части</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Что ещё часто рядом с приложением?</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>• Reverse proxy / балансировщик (nginx, ARR, HW LB) — если несколько серверов Creatio.
+• Файлы/вложения — диск сервера или объектное хранилище.
+• Почта (SMTP) — уведомления.
+• Elasticsearch / поиск — быстрый полнотекст (если включён в ландшафте).
+• Мониторинг и логи (Windows Event Log, файлы логов, APM).
+• CI/CD и артефакты пакетов.
+• Очереди сообщений (RabbitMQ, Kafka) — интеграции и фоновая обработка.
+Что сказать: перечислите 5–6 блоков и зачем каждый — уже сильный ответ.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="220" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Масштаб</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Один сервер и несколько серверов — в чём разница?</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Один сервер: IIS + приложение + иногда даже БД рядом (для учебных стендов).
+Боевой вариант чаще:
+• 2+ сервера приложения за балансировщиком;
+• отдельный SQL;
+• общий Redis, чтобы кэш/сессии видели все ноды;
+• общее файловое хранилище.
+Иначе пользователь попал на сервер A, потом на B — и «пропали» локальные файлы/кэш.
+Что сказать: «При горизонтальном масштабе нужны sticky/общие сессии и общее хранилище».</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="220" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>RabbitMQ</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Что такое RabbitMQ простыми словами?</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>RabbitMQ — почтовое отделение для программ.
+Одна программа кладёт письмо (сообщение) в очередь, другая забирает и обрабатывает, когда готова. Им не нужно быть онлайн строго в одну секунду.
+Зачем:
+• интеграции («создали заказ → потом отправим в 1С»);
+• не тормозить пользователя долгим действием;
+• сгладить пики нагрузки;
+• повторить обработку, если потребитель упал.
+Ключевые слова: producer (отправитель), queue (очередь), consumer (обработчик), exchange (куда «бросить» и как маршрутизировать).
+Что сказать: «Брокер очередей сообщений; асинхронная связь сервисов».</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="220" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>RabbitMQ</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Как устроена маршрутизация в Rabbit (очень кратко)?</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Продюсер обычно публикует не «сразу в очередь», а в exchange.
+Exchange по правилам кладёт сообщение в одну или несколько очередей.
+Консьюмер читает из очереди.
+Простые типы exchange:
+• direct — точное совпадение ключа маршрутизации;
+• topic — шаблоны вроде order.*;
+• fanout — всем очередям сразу.
+Аналогия: exchange — сортировочный центр, queue — ящик конкретного курьера.
+Что сказать: «Producer → Exchange → Queue → Consumer».</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="220" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>RabbitMQ</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Как работать с RabbitMQ на практике?</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Типовой цикл:
+1) Подняли Rabbit (Docker/сервер), создали exchange/очередь/binding.
+2) В .NET подключились клиентом (например RabbitMQ.Client).
+3) Продюсер: сериализовали JSON → BasicPublish.
+4) Консьюмер: BasicConsume → обработали → Ack (подтвердили).
+5) Если упали без Ack — сообщение можно отдать снова.
+Важные правила:
+• делайте обработку идемпотентной (повтор сообщения не должен дважды списать деньги);
+• ошибочные сообщения — в retry / dead-letter очередь, а не бесконечный цикл;
+• не держите огромные сообщения лучше класть ссылку на файл/Id в БД;
+• следите за ростом очереди (мониторинг).
+Что сказать: «Publish/consume, ack, idempotency, DLQ, мониторинг длины очереди».</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="220" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Что такое Apache Kafka простыми словами?</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Kafka — большой журнал событий (лог), который читают многие.
+Аналогия: не почтовый ящик «забрал письмо — его больше нет», а лента новостей: события дописываются в конец, разные читатели могут читать с разной скоростью и даже перечитывать историю (в пределах хранения).
+Зачем:
+• много событий (клики, изменения заказа, логи интеграций);
+• несколько систем слушают один поток;
+• нужна высокая пропускная способность и история.
+Слова: producer, topic (тема), partition (часть темы), consumer group, offset (закладка «до куда прочитал»).
+Что сказать: «Распределённый commit-log / event streaming платформа».</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="220" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Как работать с Kafka на практике?</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Типовой цикл:
+1) Создали topic (часто с несколькими partition).
+2) Продюсер пишет события в topic (ключ влияет на то, в какую partition попадёт).
+3) Консьюмер в consumer group читает свою долю partition.
+4) Сдвигает offset, когда обработал.
+В .NET часто Confluent.Kafka: Producer.Produce / Consumer.Consume.
+Правила:
+• думайте событиями («ЗаказОплачен»), а не «вызови вот тот сервис»;
+• один и тот же ключ (например orderId) помогает сохранить порядок внутри partition;
+• обработка должна переживать повтор (at-least-once — частый режим);
+• следите за lag — насколько консьюмер отстаёт от конца топика.
+Что сказать: «Пишем в topic, читаем consumer group’ой, следим за offset/lag, идемпотентность».</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="220" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Сравнение</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>RabbitMQ vs Kafka — в чём разница?</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Очень коротко:
+RabbitMQ — классическая очередь задач/сообщений.
+• сообщение обычно забрали и обработали (как письмо);
+• удобная гибкая маршрутизация (exchange);
+• отлично для команд и задач: «отправь email», «выгрузи в 1С»;
+• проще ментальная модель для многих интеграций CRM.
+Kafka — поток событий / журнал.
+• сообщения долго лежат в логе, их читают многие;
+• сильна на большом потоке событий и replay истории;
+• сложнее эксплуатация (partition, consumer group, retention);
+• отлично для event-driven архитектуры и аналитических пайплайнов.
+Грубая шпаргалка выбора:
+• нужно «сделай задачу воркеру» → чаще Rabbit;
+• нужно «запиши событие, пусть 5 систем слушают и можно переиграть» → чаще Kafka.
+Что сказать: именно эту таблицу различий + 1 пример выбора.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="218" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Сравнение</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли заменить одно другим?</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Иногда да, часто нет идеально.
+На Rabbit можно строить event-потоки, но история и огромный throughput — не его сильная сторона.
+На Kafka можно делать очереди задач, но для простых RPC-подобных задач Rabbit обычно проще.
+В корпорациях часто живут ОБА: Kafka — шина событий, Rabbit — конкретные рабочие очереди.
+Что сказать: «Инструменты с разным фокусом; выбор от паттерна нагрузки и команды эксплуатации».</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="220" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Creatio</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Где очереди встречаются рядом с Creatio?</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Типовые сценарии:
+• Creatio сохранила заявку → в очередь сообщение → отдельный воркер шлёт в ERP/шину;
+• внешняя система пишет события в Kafka → сервис-адаптер создаёт/обновляет записи в Creatio через API;
+• тяжёлые массовые операции выносят из синхронного save в фон.
+Важно для разработчика Creatio:
+• не делать долгий HTTP внутри сохранения карточки, если можно положить сообщение в очередь;
+• продумать повтор и идемпотентность (Creatio может сохранить, а ответ наружу потеряться);
+• логировать correlation id между CRM и очередью.
+Что сказать: «Очередь развязывает UI Creatio и медленные интеграции; обязательны retry и идемпотентность».</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="162" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Практика</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Что ответить, если спросят: «Расскажите архитектуру вашего стенда»?</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Шаблон ответа:
+«Снаружи пользователи ходят на балансировщик/IIS. Там крутится Creatio на .NET. Данные — в SQL/PostgreSQL. Для ускорения и общей сессии между нодами — Redis. Вложения на файловом/объектном хранилище. Для интеграций — Rabbit или Kafka (у нас был …). Логи и мониторинг отдельно. Пакеты катим dev→test→prod».
+Подставьте, что было у вас по факту. Если чего-то не было — так и скажите честно, но покажите понимание общей схемы.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="156" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Практика</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Мини-сравнение гарантий доставки.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>at-most-once — максимум один раз (можно потерять).
+at-least-once — минимум один раз (можно дубль) — самый частый.
+exactly-once — «ровно один» сложно и дорого, на практике часто делают at-least-once + идемпотентный обработчик.
+Что сказать: «Ориентируюсь на at-least-once и идемпотентность консьюмера».</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2985,13 +3511,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3120,12 +3646,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Запишите на диктофон ответ «о себе» и послушайте</t>
+          <t>Пройдите Архитектура_очереди: IIS/Redis/БД + Rabbit vs Kafka</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Убрать воду и запинки</t>
+          <t>Часто спрашивают общую схему стенда</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
@@ -3138,47 +3664,65 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>Запишите на диктофон ответ «о себе» и послушайте</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Убрать воду и запинки</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
           <t>Повторите слабые темы (колонка Статус = повторить)</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Закрепление</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Правило</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>На собесе отвечайте схемой: 1) простой смысл 2) короткий термин 3) пример</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Так звучите и понятно, и «по-взрослыму»</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D10"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
+++ b/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
@@ -18,7 +18,7 @@
     <sheet name="SQL_шпаргалка" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C#'!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C#'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SQL'!$A$1:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'JavaScript'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Creatio_BPMSoft'!$A$1:$D$16</definedName>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -851,15 +851,133 @@
     <row r="7" ht="220" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>Рефлексия vs полиморфизм</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Слушатель вроде MscCaseEventListener — это пример рефлексии?</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Коротко: почти, но так говорить на собесе НЕТОЧНО.
+MscCaseEventListener сам по себе — не «пример рефлексии». Это обычный класс-слушатель:
+• наследование от EntityEventListener;
+• override OnInserting / OnUpdating и т.д.;
+• часто атрибут вроде [EntityEventListener(SchemaName = "Case")].
+Рефлексия тут у ПЛАТФОРМЫ, не у вашего кода: при старте/сборке Creatio находит такие классы (часто по атрибутам) и подписывает их на события сущности.
+Как назвать правильно:
+• ваш listener → события / Observer + наследование + hook на жизненный цикл Entity;
+• как Creatio его подцепил → discovery по метаданным/атрибутам, внутри часто рефлексия.
+Что сказать: «Слушатель — обработчик событий сущности. Рефлексию использует платформа, чтобы найти и зарегистрировать классы с атрибутом. В самом listener я пишу обычный C#: override методов, без GetType/Invoke».
+Если сказать «listener — это рефлексия» — могут поправить. Если сказать «платформа через атрибуты и рефлексию регистрирует listener’ы» — правильно.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="220" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Полиморфизм в Creatio</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Пример полиморфизма в Creatio?</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Смысл полиморфизма: один и тот же «разъём», разное поведение.
+Пример 1. EntityEventListener
+Базовый класс говорит: есть OnInserting / OnUpdating. Ваши классы делают разное:
+public class MscCaseEventListener : EntityEventListener {
+  public override void OnInserting(...) {
+    // для Case: проверить обязательные поля
+  }
+}
+public class MscContactEventListener : EntityEventListener {
+  public override void OnInserting(...) {
+    // для Contact: проставить источник лида
+  }
+}
+Платформа вызывает один и тот же метод жизненного цикла, а срабатывает ВАША реализация. Это полиморфизм (virtual/override).
+Пример 2. Клиентские схемы JS
+Родительская страница имеет save(). Ваша replacing-схема делает save по-своему и при необходимости зовёт this.callParent(arguments).
+Что сказать: «Полиморфизм — когда платформа вызывает общий метод, а поведение подставляется классом схемы/listener’а».</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="220" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Рефлексия в Creatio</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Пример рефлексии в Creatio?</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Смысл рефлексии: узнать тип/члены во время работы и вызвать их по имени/метаданным.
+Вы сами редко пишете GetType(), но платформа — да.
+Пример 1. Как платформа находит listener
+Классы с атрибутом [EntityEventListener(SchemaName = "Case")]. Creatio сканирует сборки, читает атрибуты и регистрирует обработчики — это рефлексия/метаданные.
+Пример 2. Работа с Entity «универсально»
+entity.SetColumnValue("Name", "Иван");
+var status = entity.GetTypedColumnValue&lt;Guid&gt;("StatusId");
+Снаружи это API Entity, внутри платформа по имени колонки находит поле схемы. На собесе: «прикладной след метаданных — обращение к полям по имени, а не только через жёсткие свойства класса».
+Пример 3. «Ручная» рефлексия (редко в прикладном коде)
+var type = Type.GetType("Terrasoft.Configuration.MyService, MyPackage");
+var service = Activator.CreateInstance(type);
+type.GetMethod("Run")?.Invoke(service, null);
+В Creatio так обычно не пишут без нужды — лучше явный класс/интерфейс.
+Что сказать: «Рефлексия у платформы: атрибуты listener’ов и метаданные схемы; в моём коде чаще Entity по имени колонки, а не ручной Invoke».</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="220" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Рефлексия vs полиморфизм</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Как не перепутать рефлексию и полиморфизм? (шпаргалка)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Вопрос полиморфизма: какое поведение подставить?
+Creatio: override OnInserting, callParent, разные listener’ы.
+Аналогия: разные пульты с кнопкой «Сохранить».
+Вопрос рефлексии: что это за тип и какие у него члены?
+Creatio: поиск классов по атрибутам, работа со схемой/полями по имени.
+Аналогия: открыть инструкцию к неизвестной коробке и нажать кнопку по названию.
+Готовый ответ на собесе:
+«Полиморфизм — мои EntityEventListener с разным OnInserting. Рефлексия — сторона платформы: находит listener’ы по атрибутам и работает с метаданными схемы; в прикладном коде я чаще вижу это как работу с Entity/колонками по имени, а не как ручной Invoke».</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="220" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Интерфейсы</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Что такое интерфейс? Объясните как чайнику.</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Интерфейс — это договор.
 Пример: розетка. Неважно, чайник это или зарядка — если вилка подходит под стандарт, включится. Интерфейс говорит: «умеешь вот эти действия» — а КАК именно умеешь, каждый класс решает сам.
@@ -872,20 +990,20 @@
 Что сказать: «Контракт без реализации. Нужен для гибкости и подмены реализаций».</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="220" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="220" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Интерфейсы</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Зачем писать код через интерфейсы?</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Чтобы не привязываться к одной конкретной реализации.
 Плохо: класс жёстко создаёт new SmtpClient() внутри себя.
@@ -898,20 +1016,20 @@
 В Creatio та же мысль: сервисы, обработчики, процессы — лучше не писать «лапшу» в одном месте.</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="170" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="170" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Интерфейсы</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Что такое явное (explicit) определение интерфейса?</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Обычная реализация: метод виден на самом классе.
 Явная: метод виден только если смотреть на объект «как на интерфейс».
@@ -919,40 +1037,40 @@
 Что сказать коротко: «Метод доступен только через приведение к интерфейсу».</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="142" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="142" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Интерфейсы</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Может ли в интерфейсе быть готовый код?</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Раньше — нет, только «что уметь», без «как».
 С C# 8+ можно писать default-методы (готовая реализация прямо в интерфейсе).
 На собесе достаточно: «Классически интерфейс — контракт. В новых версиях C# добавили default interface methods, но в корпоративном коде ими не злоупотребляют».</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="220" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="220" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>ООП</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>SOLID — что это простыми словами?</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Пять правил «чтобы код не превратился в кашу»:
 S — один класс = одна задача. Не мешайте сохранение записи и отправку письма в одном монстре.
@@ -964,20 +1082,20 @@
 Что сказать: перечислите буквы своими словами + 1 пример — этого хватает.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="194" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="194" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ООП</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Инкапсуляция, наследование, полиморфизм — по-простому.</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Инкапсуляция — прячем внутренности. Как пульт: кнопки снаружи, схема внутри.
 Наследование — «ребёнок» забирает общее у «родителя» и добавляет своё.
@@ -986,20 +1104,20 @@
 Что сказать: три определения + короткий пример из жизни или из CRM.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="180" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="180" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>ООП</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>virtual, override, new — в чём разница?</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>virtual — «этот метод можно переопределить в наследнике».
 override — «я реально переопределяю поведение родителя» (настоящий полиморфизм).
@@ -1008,20 +1126,20 @@
 Что сказать: «Для полиморфизма нужны virtual/override. new лучше не использовать без нужды».</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="204" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="204" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Типы</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Value type и Reference type — чем отличаются?</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Value type (int, bool, DateTime, struct) — «само значение». Копируете переменную — копируете содержимое.
 Reference type (class, string, массивы) — «ссылка на объект в памяти». Копируете переменную — копируете адрес, оба смотрят на один объект (кроме string: строки нельзя менять, поэтому ощущение другое).
@@ -1029,20 +1147,20 @@
 Что сказать: разница в копировании и хранении + пример int vs класс Entity.</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="170" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="170" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Типы</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Что такое null и int?</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Обычный int нулём быть не может — всегда число.
 int? (nullable) — «либо число, либо пусто».
@@ -1050,20 +1168,20 @@
 Что сказать: «Nullable value types и проверки на null обязательны, особенно при чтении из БД».</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="180" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="180" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Коллекции</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>List, Dictionary, HashSet — когда что?</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>List — список по порядку, «первый, второй, третий». Как очередь номеров.
 Dictionary — словарь «ключ → значение». Быстро найти по Id. Как телефонная книга.
@@ -1072,20 +1190,20 @@
 Что сказать: выбираю структуру под задачу: порядок / поиск по ключу / уникальность.</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="220" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="220" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>LINQ</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Что такое LINQ простыми словами?</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Удобный способ спросить у коллекции: «дай где…», «преврати в…», «посчитай…».
 Where — отфильтровать.
@@ -1095,20 +1213,20 @@
 Что сказать: «LINQ — запросы к данным в коде. Where/Select, помнить про deferred execution».</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="220" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="220" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>async/await</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Что такое async/await без сложных слов?</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Когда программа ждёт ответ из интернета или БД, глупо просто «замирать и ничего не делать».
 async/await — способ сказать: «пойду ждать ответ, а поток пусть пока займётся другим».
@@ -1118,20 +1236,20 @@
 Что сказать: «Асинхронность для I/O. await не блокирует поток как Sleep».</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="208" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="208" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Исключения</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Как правильно работать с ошибками (try/catch)?</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>try — пробуем опасное.
 catch — ловим то, что умеем обработать.
@@ -1141,20 +1259,20 @@
 В Creatio: пользователю — ясно «почему не сохранилось», в лог — подробности для разработчика.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="170" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="170" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>IDisposable</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Зачем using и Dispose?</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Некоторые вещи нужно обязательно закрыть: файл, соединение с БД.
 using сам закроет даже если случилась ошибка.
@@ -1162,20 +1280,20 @@
 Что сказать: «IDisposable + using для детерминированного освобождения ресурсов».</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="170" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="170" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Почему StringBuilder, а не string + string в цикле?</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>string нельзя «дописать» — каждый раз создаётся новая строка.
 В цикле из тысяч сложений это тормозит и жрёт память.
@@ -1183,40 +1301,40 @@
 Что сказать: «string immutable; для частых конкатенаций — StringBuilder».</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="156" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="156" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Generics</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Что такое generics?</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Шаблон с типом-параметром: List&lt;int&gt;, List&lt;string&gt; — один код, разные типы, без каши из object.
 Плюс: типобезопасность (компилятор ругается раньше) и без лишних упаковок для чисел.
 Что сказать: «Обобщения дают переиспользование без потери типов».</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="156" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="156" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>События</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>delegate, event, Action, Func — кратко.</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Делегат — «ссылка на метод».
 Action / Func — готовые удобные делегаты (сделай что-то / сделай и верни).
@@ -1224,20 +1342,20 @@
 Аналогия: event — кнопка звонка в подъезд; жильцы подписываются на «кто-то звонит».</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="220" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="220" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Creatio C#</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Как в Creatio работать с записью (Entity)?</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Простыми шагами:
 1) Берём подключение пользователя (UserConnection) — «я работаю от имени системы/юзера».
@@ -1249,20 +1367,20 @@
 Что сказать: «Через Entity/UserConnection: Fetch → SetColumnValue → Save; учитываю права».</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="220" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="220" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Creatio C#</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>EntitySchemaQuery или голый SQL — что выбрать?</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>ESQ — «правильный» способ платформы спросить данные: учитывает права, схемы, безопаснее.
 Прямой SQL — когда очень сложный отчёт или нужно быстрее/гибче, но:
@@ -1273,20 +1391,20 @@
 Что сказать именно так — звучит зрело.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="220" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="220" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Creatio C#</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Что такое EntityEventListener?</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Это «сторож» на события записи: перед/после добавления, изменения, удаления.
 Примеры:
@@ -1294,23 +1412,24 @@
 • при создании контакта дописать поле «Источник».
 Важно: не устраивать вечный цикл Save → событие → снова Save.
 Тяжёлые внешние вызовы в событии — осторожно (может тормозить сохранение).
+На собесе не путайте с рефлексией: сам listener — это полиморфизм (override OnInserting). Рефлексию использует платформа, чтобы НАЙТИ ваш класс по атрибуту. Подробнее — лист C#, блок «Рефлексия vs полиморфизм».
 Что сказать: «Подписка на жизненный цикл Entity для валидаций и побочной логики».</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="194" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="194" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Creatio C#</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Процесс Creatio или C#-код — когда что?</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Процесс (визуальный BPM) — когда шаги понятны бизнесу: согласование, письмо, ждать 2 дня, развилка.
 C# — когда сложный алгоритм, интеграция, производительность, много переиспользования.
@@ -1318,20 +1437,20 @@
 Что сказать: «Low-code для оркестрации, код для сложной логики».</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28" ht="208" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="208" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Практика</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Как искать баг «поле иногда не сохраняется»?</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Не гадайте — идите по чеклисту:
 1) Воспроизвести под той же ролью, что у пользователя.
@@ -1342,20 +1461,20 @@
 Что сказать: показать системный подход. Это ценится больше, чем «я сразу знаю причину».</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29" ht="184" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="184" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Делегаты vs интерфейсы</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Когда делегат, когда интерфейс?</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Делегат/Action — одна простая реакция: «когда готово — вызови вот это».
 Интерфейс — набор связанных умений и нормальный объект с жизнью.
@@ -1364,40 +1483,40 @@
 Что сказать: «Делегат для колбэка, интерфейс для зависимости с несколькими операциями».</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="156" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="156" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Equals</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Зачем Equals и GetHashCode вместе?</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Если кладёте объекты в Dictionary/HashSet как ключи, сравнение и хеш должны быть согласованы: равные объекты → одинаковый hash.
 В CRM обычно равенство записей — по Id (Guid), а не по всем полям.
 Что сказать: «Пара должна быть согласована; для Entity сравниваем по Id».</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="180" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="180" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Потоки</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Что такое race condition и lock?</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Race — два потока одновременно портят общие данные, как два человека правят один Excel.
 lock — «сейчас работает только один, остальные подождут».
@@ -1405,10 +1524,10 @@
 Что сказать: «Гонка за общее состояние; синхронизация через lock/concurrent-коллекции; static mutable — риск».</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D31"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
+++ b/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
@@ -16,6 +16,12 @@
     <sheet name="Резюме_и_поведение" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Как_готовиться" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="SQL_шпаргалка" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Ваши_C#" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ваши_SQL" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Ваши_JS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Ваши_Creatio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Ваши_Creatio_админ" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Ваши_WEB" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C#'!$A$1:$D$35</definedName>
@@ -25,6 +31,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Архитектура_очереди'!$A$1:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Резюме_и_поведение'!$A$1:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Как_готовиться'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Ваши_C#'!$A$1:$E$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Ваши_SQL'!$A$1:$E$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ваши_JS'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ваши_Creatio'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ваши_Creatio_админ'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Ваши_WEB'!$A$1:$E$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +45,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +65,16 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -99,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,6 +138,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -691,7 +717,6440 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Добавлено из ваших файлов</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Лист</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Откуда</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Q&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ваши_C#</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Собес имени меня + Собеседование (уникальные)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ваши_SQL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Собес имени меня + Собеседование (уникальные)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ваши_JS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Собес имени меня + Собеседование (уникальные)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ваши_Creatio</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Собес имени меня + Собеседование (уникальные)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ваши_Creatio_админ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Собес имени меня + Собеседование (уникальные)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ваши_WEB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Собес имени меня + Собеседование (уникальные)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Как пользоваться</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Сначала листы C#/SQL/… (учебные ответы «для чайников»), затем листы «Ваши_*» — ваши билеты. Пустые ответы заполнены простым текстом; где было «[заготовка]» — допишите по резюме.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E134"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Ответ простыми словами</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="156" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Dependency Injection - внедрение зависимостей
+Для чего нужен паттерн</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Данные на которые ссылается переменная не могут быть изменены. Внимание: значение переменной может быть изменено, но в таком случае 
+данные помеченные как immutable уничтожаются и новвые данные создаются в памяти. происходит на этапе выполнения.  
+string a = "Привет";
+string b = a;
+b = "Мир";
+Console.Writeline(a);
+Выведется "Привет" - string immutable тип</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="76" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>DIP- Инверсия зависимостей</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Модули верхнего уровня не должны зависеть от модулей нижнего уровня. И те и другие должны зависеть от абстракций. Абстракции не должны зависеть от деталей. Детали должны зависеть от абстракций.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="200" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>GC, using, dispose.
+В какую конструкцию разворачивается using ? Напишие аналог using-секции
+Отличие Dispose от Finalize</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>try -&gt;  p = new Person() -&gt; finally -&gt;  if (p != null) p.Dispose();
+Разница в том, что время вызова финализатора не определено. Стоит также отметить, что если Dispose предназначен для вызова вручную, то финализатор вручную вызвать нельзя. Это делается автоматически.
+Существует 0, 1 и 2 поколение - 0 самые новые.
+Если у объекта есть финализатор, то он не удаляется сразу, как только сборщик мусора решит, что он больше не нужен.
+Куча больших объектов (Large Object Heap, LOH), в которой размещаются объекты размером от 85000 байт.
+Исключение OutOfMemoryException, вызванное фрагментацией, обычно происходит, когда программа имеет много свободной памяти, но из-за фрагментации не может разместить в ней новый объект.
+Финализаторы - объекты этих классов не могут быть удалены немедленно, вместо этого они попадают в очередь финализаторов и удаляются из памяти только после того, как финализатор будет выполнен.
+Dispose(GC.SuppressFinalize())</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="84" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>IOC контейнер</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Паттерн, в котором управление объектом (в нашем случае – временем жизни объекта) поручено какой-то компоненте. Некий такой аутсорс – вместо того чтобы создавать объект самим (через new()) мы запрашиваем его у т.н. IoC-контейнера, то есть у фабрики, которая умеет грамотно производить объекты.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="128" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Reflection для чего?
+Каим образом можно получить список полей, свойств и методов класса?
+Каким образом можно получить список конструкторов и выбрать конструктор по-умолчанию?</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Рефлексия представляет собой процесс выявления типов во время выполнения приложения.
+GetConstructors()
+GetFields() 
+GetInterfaces() 
+GetMethods()
+System.Attribute</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>String и StringBuilder отличия</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Строку нельзя изменить, string builder нужен когда складывать много строк, чтобьы не переполнять память. Чтобы на каждый + не создавалась новая строка. + под капотом компилируется string.concat</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="108" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Асинхранная функция какие типы может возвращать? 5 типов
+Что теряешь если возращаешь void
+Какие требования накладываются на ValueTask</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Task, Task&lt;&gt;, void, ValueTask, ValueTask&lt;&gt;, Async string
+Асинхронная операция пошла и мы её не ожидаем, если исключение выпадет оно не вызовется в программе, подходит для лоширования.
+ValueTask - определёт в стеке не вызывает аллокаций, не нужно выделять память в куче и не нужно вызывать GC.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="68" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Асинхронная программа, разные потоки стучатся в singleton. Что нужно обеспечить?</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Обеспечить синхронизации потоков. Чтобы ресурсы использовал только 1 поток. Если с числами работаем InterLosket. Конкурентные коллекции. ConcurrentDictionary, Stack</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="104" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Будет ли выполнен блок finally, если не было сгенерировано исключение ?</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Да, finally почти всегда выполняется (и при успехе, и при ошибке), кроме жёсткого убийства процесса.
+Что сказать: «finally выполняется в любом случае».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="112" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>В какой момент применяется условие отбора, указанное в методе расширения .Where(x=&gt;….) ? Можно ли это изменить ?</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>У IEnumerable — при перечислении (лениво). У IQueryable — когда запрос материализуется (ToList/foreach), и условие может уйти на сервер.
+Что сказать: «Deferred execution до материализации».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="104" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>В какой момент срабатывает статический конструктор класса ?</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Перед первым обращением к типу (создание или static-член), ровно один раз, потокобезопасно.
+Что сказать: «Один раз до первого использования типа».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="112" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>В каком случае вы обязаны использовать модификатор abstract ?</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Когда в базовом классе есть члены без реализации — класс обязан быть abstract, иначе компилятор не даст «недоделанный» обычный класс.
+Что сказать: «Есть abstract-члены → класс abstract».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="104" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>В какую конструкцию разворачивается using ? Напишие аналог using-секции</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>try { ... } finally { if (x != null) x.Dispose(); } (упрощённо).
+Что сказать: «try/finally + Dispose».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="116" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>В чем отличие Func&lt;string&gt; от Expression&lt;Func&lt;string&gt;&gt; ?</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Func — готовый делегат для выполнения.
+Expression&lt;Func&gt; — описание выражения для анализа провайдером.
+Что сказать именно так.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="116" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>В чем отличие абстрактного класса от интерфейса ?</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Абстрактный класс — это класс, у которого не реализован один или больше методов (некоторые языки требуют такие методы помечать специальными ключевыми словами).
+Используется для хранения state, можно создавать int переменные, которые хранятся в экземпляре класса. Используется без функциональности для сущностей, для передачи полей.
+Интерфейс — это абстрактный класс, у которого ни один метод не реализован, все они публичные и нет переменных класса.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собес имени меня + Собеседование</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="104" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>В чем разница между IDictionary.Add(key, value) и IDictionary[key] = value</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Add — если ключ есть, exception. indexer[] = — вставит или перезапишет.
+Что сказать именно так.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="116" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>В чем разница между абстрактными и виртуальными методами ?</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>abstract — обязательно переопределить, реализации в базе нет.
+virtual — реализация есть, переопределение по желанию.
+Что сказать именно так.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="104" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание Array</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Массив — фиксированная длина, доступ по индексу.
+Что сказать: «Фиксированная длина, быстрый индекс».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="104" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание Delegate и Multicast Delegate.</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Delegate — ссылка на метод. Multicast — несколько методов в одной цепочке (+=).
+Что сказать: «Тип для колбэка; multicast вызывает всех подписчиков».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="104" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание Event</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>event — обёртка над делегатом: снаружи только +=/-=, вызвать чужой event нельзя.
+Что сказать: «Безопасная подписка на уведомления».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="104" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание Expression</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Expression Tree — дерево выражения, которое можно разобрать (EF/SQL), а не сразу выполнить как делегат.
+Что сказать: «Данные о коде, а не сам выполняемый код».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="124" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание Extension-методов. Как объявить метод расширения ?</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Метод расширения: static-класс + this Type у первого параметра: public static int WordCount(this string s).
+Вызов как у обычного метода: "hi".WordCount().
+Что сказать: «Синтаксический сахар для static-метода с this».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="104" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание IDictionary&lt;TKey,TValue&gt;</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Словарь ключ→значение с быстрым поиском.
+Что сказать: «Ассоциативный массив».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="104" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание IDisposable. Для чего применяется ?</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Контракт «закрой ресурс»: файлы, соединения. using вызовет Dispose.
+Что сказать: «Освобождение ресурсов детерминированно».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="104" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание IEnumerable, IEnumerator?</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>IEnumerable — можно перебрать. IEnumerator — Current/MoveNext.
+Что сказать: «Последовательность и её перечислитель».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание immutable.</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Неизменяемый тип</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="124" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание IQueryable. В чем ключевое отличие от IEnumerable ?</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>IQueryable — выражение для провайдера (часто SQL). IEnumerable — уже в памяти CLR.
+Where на IQueryable может уйти в SQL; на IEnumerable фильтрует в процессе.
+Что сказать: «IQueryable строится в запрос к источнику; IEnumerable — локально».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="104" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание Linq</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Удобный язык запросов к коллекциям/провайдерам: Where, Select, Join…
+Что сказать: «Запросы к данным в коде».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="104" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание абстрактного класса</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Класс-заготовка: может иметь реализацию и abstract-методы. Экземпляр напрямую не создают.
+Что сказать: «Частично реализованный базовый тип».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="104" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание анонимного метода, lambda-выражений</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Анонимный метод / lambda — функция без имени: x =&gt; x * 2, удобно для LINQ и событий.
+Что сказать: «Короткий безымянный обработчик/функция».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="104" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание инструкций is и as</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>is — проверка типа. as — безопасный cast для reference (иначе null).
+Что сказать: «is = проверка, as = null при неудаче».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="104" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание интерфейса</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Контракт: что уметь, без как. Класс может реализовать много интерфейсов.
+Что сказать: «Договор о поведении».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание ключевого слова default</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>По умолчанию</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание ключевого слова params</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Можно передавать однотипные данные, а они приходят в массиве.</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="104" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание коллекций и списков</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Коллекции — List, Dictionary, HashSet… List — динамический массив.
+Что сказать: «Готовые структуры данных под задачу».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание модификаторов ref и out</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Передаём по ссылке</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="104" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание обобщенных (generic) типов</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Generics — типы с параметром T: List&lt;int&gt;. Типобезопасность без кастов.
+Что сказать: «Переиспользование кода с сохранением типов».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="68" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание обобщенных (generic) типов
+Какую проблему решали обобщенные коллекции ?</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Необобщенные классы коллекций, в отличие от обобщенных, не обеспечивают безопасность типов, простоту и понятность кода и повышение производительности.</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="104" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание ограничений параметров обобщенных типов</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>where T : class, new(), IDisposable — ограничения на T.
+Что сказать: «where ограничивает допустимые T».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="104" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание операций ? и ??</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>?: тернарный if. ?? — если null, взять справа. ?. — безопасный доступ.
+Что сказать: «?? и ?. для null-безопасности».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="112" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание паттерна Abstract Factory</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Abstract Factory — фабрика фабрик: семейства связанных объектов без указания конкретных классов.
+Что сказать: «Создаём набор связанных продуктов через абстрактную фабрику».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="104" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание паттерна Builder</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Builder — пошаговая сборка сложного объекта (цепочка SetX().SetY().Build()).
+Что сказать: «Строим сложный объект по шагам, чтобы конструктор не раздувался».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="124" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание паттерна Factory Method</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Factory Method — метод создания объекта вынесен в наследников.
+В Creatio похожий дух у ClassFactory / создания Entity по имени схемы.
+Что сказать: «Создание объекта делегируем методу/фабрике, а не new по всему коду».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="104" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание перегрузки методов</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Одно имя метода, разные наборы параметров. Компилятор выбирает подходящую перегрузку.
+Что сказать: «Одно имя — разные сигнатуры».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="104" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание понятия Исключительная ситуация (Exception)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Exception — сигнал ошибки, который можно поймать и обработать, а не молча получить неверные данные.
+Что сказать: «Объект ошибки с типами и стеком вызовов».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="172" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание принципа SOLID</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Single Responsibility Principle (Принцип единственной обязанности) У класса должна быть только одна причина для изменения
+Open/Closed Principle (Принцип открытости/закрытости) Сущности программы должны быть открыты для расширения, но закрыты для изменения.
+Liskov Substitution Principle (Принцип подстановки Лисков) Должна быть возможность вместо базового типа подставить любой его подтип
+Interface Segregation Principle (Принцип разделения интерфейсов) Клиенты не должны вынужденно зависеть от методов, которыми не пользуются
+Dependency Inversion Principle (Принцип инверсии зависимостей) Модули верхнего уровня не должны зависеть от модулей нижнего уровня. И те и другие должны зависеть от абстракций. Абстракции не должны зависеть от деталей. Детали должны зависеть от абстракций.</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собес имени меня + Собеседование</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="68" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание работы класса StringBuilder. Есть ли преимущество перед использованием String ?</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>При прибавлении к строке создается новая переменная с результатом конкатенации, а в StringBuilder результат записывается в одну переменную.</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="104" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание рекурсии</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Функция вызывает себя + условие выхода.
+Что сказать: «Самовызов + база рекурсии».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="104" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание секции using (var value = ...)</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>using создаёт область и гарантирует Dispose в finally.
+Что сказать: «Авто-Dispose даже при ошибке».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание статического класса</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Не требует создания экземпляра класса, его нет</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание статического метода</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Не нужно создавать экзепляр класса, можно обращаться на прямую к классу.</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="124" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание упаковки (Boxing) и распаковки (Unboxing). Приведите пример.</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Boxing — упаковать value type в object (аллокация в куче). Unboxing — обратно с кастом.
+Пример: object o = 5; int x = (int)o;
+Что сказать: «Упаковка значимого типа в object; лучше generics без boxing».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="104" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Возможно ли множественное наследование интерфейсов в C# ?</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Да, класс/интерфейс может наследовать много интерфейсов.
+Что сказать: «Да».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55" ht="104" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Возможно ли множественное наследование классов в C# ?</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Классов — нет (только один родитель). Интерфейсов — да, сколько угодно.
+Что сказать именно так.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="116" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Возможно ли разрешить наследование класса, но запретить перекрытие метода?</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>sealed override — наследник не сможет дальше override.
+Класс можно оставить не-sealed.
+Что сказать: «sealed на override-методе».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="136" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Дан код:
+ public class Node { public Node Parent {get;set;} public string Name {get;set;} public IEnumerable Children{get;set;} }
+ У корневого узла Parent всегда равен null;
+ Предоставлен корневой узел дерева, содержащий несколько уровней
+ Node root = ReadXml();</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Дерево узлов Parent/Children. Корень — Parent == null.
+Уровень: идём вверх по Parent, считаем шаги.
+Обход: печатаем уровень+имя, рекурсивно дети.
+Что сказать: «Self-reference Parent + рекурсия по Children».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="112" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Дан код:
+ try { DoWork(); return 1; } catch(Exception ex) { Log(ex); return 2; } finally { return 3; }</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Если в finally есть return — он перебивает return из try/catch (плохой стиль, так не пишите).
+Что сказать: «return в finally перекрывает предыдущий; на практике return в finally не используют».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="104" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Дан код:
+ var dictionary = new Dictionary&lt;string, string&gt;();
+ …..
+ foreach(var item in dictionary){}
+ Какой тип у item ?</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Во время foreach нельзя менять состав словаря (Add/Remove).
+Что сказать: «Не модифицировать коллекцию в foreach».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Дан массив строк 
+ var strArray = new[]{"Str1","Str2","Str3"……"Str1000"}
+ Какими механизмами вы воспользуетесь для формирования строки, содержащей все элементы массива с разделителями ? Почему именно эти механизмы ?</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>string.Join()</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61" ht="104" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Дан следующий код:
+ var value = 1;
+ 1: var result = (TType)value;
+ 2: var result = (value as TType)</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>as обычно для reference types. Не тот тип → null без exception.
+Что сказать: «as → null при неудаче».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="104" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Даны два интерфейса:
+ public interface IWorkerA { int DoWork(); }
+ public interface IWorkerB { int DoWork(); }
+ Каким образом реализовать оба интерфейса в одном классе
+ public class Worker: IWorkerA, IWorkerB {} ?</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Если два интерфейса с одинаковым методом — один общий метод или explicit-реализация.
+Что сказать: «Общий метод или explicit».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="80" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Есть ли отличие в catch(Exception e){throw e;} и  catch(Exception e){throw;} ?</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>throw e сбрасывает трассировку стека (поэтому ваши ошибки будут возникать из HandleException)
+throw нет - исходный нарушитель будет сохранен.</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Вопросы для собеса + Собес имени меня + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="104" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Как вызвать сборщик мусора из кода, в каких случаях это целесообразно?</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>GC.Collect() вручную почти никогда не нужно — только в редких диагностических случаях.
+Что сказать: «Обычно не вызываю; доверяю runtime».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65" ht="112" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Как происходит сборка мусора в .NET?</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>GC ищет объекты без ссылок и освобождает память. Поколения 0/1/2, есть LOH для больших объектов.
+Что сказать: «Автоматическая очистка недостижимых объектов поколений».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="104" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Как создать юнит-тест?</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Test-проект (xUnit/NUnit) + Arrange-Act-Assert.
+Что сказать: «Отдельный test-проект и AAA».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Какие методы класса Object вы знаете ?</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Equals, GetHashCode, ToString, GetType</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собес имени меня + Собеседование</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Какие типы могут быть использованы в качестве значений перечисления ?</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>byte, int, short, long</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69" ht="112" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Какое значение будет возвращено в случае возникновения исключительной ситуации в методе DoWork ?</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>В коде try { DoWork(); return 1; } catch { return 2; } finally { return 3; } вернётся 3 — return в finally перекрывает. Так писать нельзя.
+Что сказать: «finally с return перебивает; на практике return в finally не используют».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70" ht="104" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Какое значение будет возвращено в случае если метод DoWork отработает без ошибок ?</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>При том же коде с return в finally снова вернётся 3, даже если DoWork успешен.
+Что сказать: «Снова 3 из finally; это плохой стиль».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71" ht="124" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Какую проблему решали обобщенные коллекции ?</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>До generics был ArrayList на object → касты, boxing, ошибки типов в runtime.
+List&lt;T&gt; даёт типобезопасность и скорость.
+Что сказать: «Убрали касты/boxing, сделали безопаснее и быстрее».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72" ht="120" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Многопоточность - данные надо защищать. Какие примитивы синхронизации знаешь?
+Simafor and simafor slim</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Примитов lock, monitor, mutex, simafor, barer
+Можем задавать количество потоков, которые могут одновременно работать в критической секции кода. Simafor работает между потоками.
+Mutex - работает только 1 поток и работает между процессами.
+Barer - устанавливаем шлагбаум и дальше потоки не могут идти пока все не дойдут до места установки.</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="200" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Многопоточность, Класс Thread.Task. Асинхронные методы
+Как проводится синхронизация потоков?
+Что такое пул потоков, как с ним работать ?
+Является ли статический конструктор или статическая инициализация полей  потоко-безопасным?
+Ваше понимание выражения lock(value), в какую конструкцию разворачивается lock?
+Ваше понимание Asyn Await. Что такое SynchronizationContext ?</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Thread - многопоточность
+Асинхронность позволяет вынести отдельные задачи из основного потока в специальные асинхронные методы и при этом более экономно использовать потоки.
+Запуск операции без ожидания ее завершения.
+Если асинхронная операция не завершена, то сохраняется код, который надо будет вызвать по завершении асинхронной операции (т.н. продолжение), а поток возвращается в пул потоков и становится доступен для использования.
+Task.Factory.StartNew(action, TaskCreationOptions.LongRunning) - для длительных операций
+Помогает ассинхронные запросы выдать. Помогать в операциях работы с БД. Мы отправили запрос на сервер мы в этот момент, поток не ждёт ответа от сервера, поток возвращается в пул потоков и он может быть переиспользован, и когда прийдет ответ от сервера поток возьмётся из пула и продолжит выполнение.</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74" ht="96" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Могут ли структуры (struct) иметь статический конструктор ?</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Да, static constructor у struct допустим.
+Что сказать: «Да».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="104" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Могут ли структуры (struct) имплементировать интерфейсы ?</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Да, struct может реализовывать интерфейсы (но будет boxing при приведении к интерфейсу).
+Что сказать: «Да, с оговоркой про boxing».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76" ht="104" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Могут ли структуры (struct) содержать события (event) ?</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Да, могут объявлять event, но mutable struct + event — осторожно.
+Что сказать: «Технически да».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77" ht="112" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Могут ли структуры содержать только конструкторы с параметрами ?</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>У struct всегда есть неявный конструктор по умолчанию (обнуление). Явный безпараметровый historically ограничен версиями.
+Что сказать: «Есть default-инициализация нулями; детали зависят от версии C#».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78" ht="80" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор abstract</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Экземпляры такого типа создавать нельзя. Член необходимо переопределить и реализовать в производном типе — только после
+этого можно создавать экземпляры производного типа</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Вопросы для собеса + Собес имени меня + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79" ht="104" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор internal</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>internal — видно внутри этой же сборки (assembly).
+Что сказать: «Доступ на уровне проекта/сборки».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80" ht="104" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор new</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>new на методе — скрывает одноимённый метод базы (не полиморфизм). Лучше virtual/override.
+Что сказать: «Скрытие имени, не override».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81" ht="104" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор private</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>private — только внутри этого класса.
+Что сказать: «Максимальная инкапсуляция».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82" ht="104" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор protected</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>protected — видно в классе и наследниках, снаружи «как private».
+Что сказать: «Для иерархии наследования».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83" ht="104" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор protected internal</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>protected — видно в классе и наследниках, снаружи «как private».
+Что сказать: «Для иерархии наследования».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84" ht="104" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор sealed</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>sealed на классе — нельзя наследовать. sealed override — нельзя дальше переопределять метод.
+Что сказать: «Запрет наследования/дальнейшего override».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85" ht="68" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор static</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Используется для объявления статического члена, принадлежащего собственно типу, а не конкретному объекту.</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86" ht="104" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Модификатор virtual</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>virtual — метод можно переопределить в наследнике через override (полиморфизм).
+Что сказать: «Разрешает полиморфное переопределение».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87" ht="104" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Может ли Delegate принимать значение null ?</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Да, делегат может быть null. Перед вызовом проверяйте или используйте ?.Invoke().
+Что сказать: «Может быть null — проверяем перед вызовом».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88" ht="104" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Может ли Event принимать значение null ?</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Поле делегата события может быть null, если никто не подписан.
+Что сказать: «Да, если нет подписчиков».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Может ли значение типа DateTime принимать значение null ?</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Нет не может он является значимым типом.</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90" ht="104" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Может ли интерфейс содержать делегаты ?</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Интерфейс может объявлять events; обычные instance-поля — нет.
+Что сказать: «Events да; instance-поля нет».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91" ht="96" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Может ли интерфейс содержать события (Event) ?</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Да, интерфейс может объявлять event.
+Что сказать: «Да».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92" ht="104" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Может ли класс одновременно иметь модификаторы asbtract и sealed ?</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Нет, abstract и sealed одновременно на классе нельзя — противоречие.
+Что сказать: «Нельзя».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93" ht="104" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли вызвать деструктор класса принудительно ?</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Напрямую вызвать нельзя. GC.Collect/WaitForPendingFinalizers — почти антипаттерн.
+Что сказать: «Принудительно не вызывают».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="104" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли выполнить несколько блоков catch для одного оператора try ?</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Да, несколько catch подряд от частного к общему. Сработает один подходящий.
+Что сказать: «Несколько catch, один сработает».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="104" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли добавить дополнительную обработку при подписывании делегата на событие ?</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Можно обернуть add/remove у event (custom event accessors) и добавить логику.
+Что сказать: «Кастомные add/remove у event».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="104" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли написать несколько блоков catch для одного оператора try ?</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Да, несколько catch подряд от частного к общему. Сработает один подходящий.
+Что сказать: «Несколько catch, один сработает».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="112" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли объявить деструктор класса ? Если да, то наследуются ли деструкторы ?</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Да, ~MyClass() — это finalizer. Наследовать «вызов цепочки» особенный; руками обычно не пишут без нужды.
+Что сказать: «Деструктор = finalizer, лучше IDisposable».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="96" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли объявить деструктор структур ?</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Нет, у struct деструктора/finalizer нет.
+Что сказать: «Нельзя».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Назовите класс .NET, от которого наследуются все классы?</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100" ht="124" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Напишите Extension-метод, возвращающий Уровень текущего узла относительно корня</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Метод расширения: static-класс + this Type у первого параметра: public static int WordCount(this string s).
+Вызов как у обычного метода: "hi".WordCount().
+Что сказать: «Синтаксический сахар для static-метода с this».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101" ht="104" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Напишите метод рекурсивного обхода дерева, выводящий на консоль узлы в формате Уровень-Наименование</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Печатаем уровень+имя, затем рекурсивно дети с level+1.
+Что сказать: «Обход: узел → дети».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102" ht="112" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Наследуются ли члены класса с модификатором private ?</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Формально поля есть в объекте наследника, но доступа к ним из кода наследника нет. Наследник их «не видит».
+Что сказать: «Недоступны наследнику, хотя физически в объекте присутствуют».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103" ht="104" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Объясните разницу между System.Array.CopyTo() и System.Array.Clone()</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Clone — новый массив (поверхностная копия). CopyTo — копирует в уже существующий.
+Что сказать: «Clone создаёт новый, CopyTo пишет в целевой».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="104" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Объясните разницу между нитью (Thread) и процессом (Process)</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Процесс — изолированная программа с памятью. Потоки — исполнители внутри процесса, делят память.
+Что сказать: процесс = изоляция, потоки = параллельность внутри.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105" ht="144" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Одиночка (Singleton)</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Singleton — в системе один экземпляр класса.
+В многопотоке нужна потокобезопасная инициализация (Lazy&lt;T&gt;, lock).
+В веб/Creatio осторожно: static на сервере общий для всех запросов.
+Что сказать: «Один экземпляр + потокобезопасность; в web static — риск».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="104" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Опишите CIL</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>CIL/IL — промежуточный код, в который компилируется C#. Потом JIT делает машинный код.
+Что сказать: «Промежуточный язык .NET до JIT».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107" ht="84" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Опишите CLR</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Общеязыковая среда выполнения (Common Language Runtime, CLR) — говорит само за себя: это среда выполнения, которая подходит для разных языков программирования. Основные возможности CLR (управление памятью, загрузка сборок, безопасность, обработка исключений, синхронизация)</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собес имени меня + Собеседование</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="104" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Опишите CLS</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>CLS — правила, чтобы разные .NET-языки могли дружить в одной экосистеме.
+Что сказать: «Общий набор правил совместимости языков».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109" ht="104" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Опишите FCL</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>FCL — библиотека классов .NET (коллекции, IO, сеть, и т.д.), то на чём пишем каждый день.
+Что сказать: «Стандартная библиотека классов Framework/BCL».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110" ht="124" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Опишите процесс перехвата исключительных ситуаций</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>try { опасное } catch (SpecificEx) { обработка } finally { уборка }.
+Ловите конкретное, логируйте, не глотайте Exception без нужды.
+Что сказать: try/catch/finally + конкретные типы.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111" ht="124" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Опишите различие между readonly полями и контстантами.</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>const — значение на этапе компиляции, только примитивы/строка.
+readonly — можно задать в конструкторе, потом не менять.
+Что сказать: const compile-time, readonly runtime в конструкторе.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112" ht="112" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Отличие Dispose от Finalize</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Dispose — явный/быстрый. Finalizer (~Class) — запасной путь от GC, момент непредсказуем; после Dispose вызывают GC.SuppressFinalize.
+Что сказать: Dispose сейчас, Finalizer — страховка GC.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113" ht="92" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Отличие ссылочного значения от значимого</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Value type хранится в основном в стеке, ограничение 4 мб, если передаём value type в методы то они копируются, если referance type по ссылке и он по памяти не ограничен. Он ограничен опертивной памятью. Value type очищается когда выходим из функции из стека забирается методом pop. Referance type в памяти удаляет GC. Value type может хранится в стеке если добавлен в класс.</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Перечисления (Enum) это Value type или Reference type ?</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Value type</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115" ht="124" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Перечислить какие типы относятся к ссылочным и значимым?</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Значимые: int, bool, DateTime, struct, enum.
+Ссылочные: class, string, массивы, делегаты.
+Что сказать: value копируется, reference передаёт ссылку на объект в куче.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116" ht="132" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Стратегия</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Паттерн Strategy: выносим алгоритм в отдельные классы с общим интерфейсом и подменяем их.
+Пример: разные способы расчёта скидки. В Creatio — разные обработчики/сервисы вместо гигантского if.
+Что сказать: «Взаимозаменяемые алгоритмы за общим интерфейсом».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Строки (String) это Value type или Reference type ?</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Это ссылочный тип</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118" ht="136" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Чем перекрытый метод отличается от перегруженного метода ? А от переопределенного ?</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Перегрузка (overload) — одно имя, разные параметры.
+Переопределение (override) — новая реализация virtual/abstract в наследнике.
+Перекрытие (new) — скрытие метода базы.
+Что сказать: overload ≠ override ≠ new.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="68" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Чем управляемый код отличается от неуправляемого.</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Неуправляемый код не происходит очистки GC. Просто при работе с ним все действия по использованию памяти, в том числе по ее очистке, ложится целиком на нас, а не на среду CLR</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="104" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Что можно использовать в качестве аргумента в конструкции foreach ?</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Тип с GetEnumerator() / IEnumerable.
+Что сказать: «IEnumerable или подходящий GetEnumerator».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121" ht="104" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Что произойдет если в выражении (TType)value, значение value не приводимо к типу TType ?</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Жёсткий cast (T)x при неудаче → InvalidCastException. as → null.
+Что сказать: «(T) — exception; as — null».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="104" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Что произойдет если в выражении (value as TType), значение value не приводимо к типу TType ?</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>as обычно для reference types. Не тот тип → null без exception.
+Что сказать: «as → null при неудаче».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123" ht="104" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Что произойдет если в выражении (value as TType), значение value является Reference Type, не приводимым к TType ?</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>as обычно для reference types. Не тот тип → null без exception.
+Что сказать: «as → null при неудаче».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="104" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Что произойдет если в выражении (value as TType), значение value является Value Type ?</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>as обычно для reference types. Не тот тип → null без exception.
+Что сказать: «as → null при неудаче».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125" ht="68" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Что происходит в процессе конкатенации строк ?</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Создается новая переменная и в неё записывается результат. Для конкатенации больше подходит StringBuilder</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126" ht="68" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Что такое .NET framework ?</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Общеязыковая исполняющая среда common language runtime (CLR) + и библиотека классов framework class library (FCL). Это фреймворк разработки программного обеспечения и сайтов</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собес имени меня + Собеседование</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127" ht="112" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Что такое GAC ? Какую проблему он разрешает?</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>GAC — Global Assembly Cache: общие сборки для машины (сильнее актуально для старого .NET Framework).
+Что сказать: «Общий кэш сборок машины; в .NET Core/5+ почти не используют».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128" ht="76" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Что такое Value Type и Reference Type ? Назовите различия между ними.</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Значимые типы хранятся в стеке, а ссылочные в куче. При передаче значимых типов значение копируется, а при передаче ссылочных передается ссылка.  Для передачи значимых типов по ссылке используются модификаторы ref, out</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="104" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Что такое класс?</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Класс — чертёж объекта: поля + поведение. Экземпляр — конкретный объект по этому чертежу.
+Что сказать: «Шаблон для объектов с данными и методами».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="124" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Что такое куча и стек? Различия, принцип работы.</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Стек — быстрая память кадров методов (локальные value, ссылки).
+Куча — объекты reference-типов, чистит GC.
+Что сказать: стек = кадры вызовов, куча = объекты под GC.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131" ht="104" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Что такое потокобезопасность ?</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Корректная работа при одновременном доступе нескольких потоков (без гонок и битых данных).
+Что сказать: «Нет гонок за общее состояние».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132" ht="104" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Что такое сборка (Assembly) ?</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Assembly — dll/exe с кодом и метаданными, единица развёртывания .NET.
+Что сказать: «Скомпилированный модуль с типами и манифестом».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="104" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Что такое частные и общие сборки ?</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Частная — рядом с приложением. Общая — в GAC/shared, версия сильным именем.
+Что сказать: private vs shared/GAC.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134" ht="104" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>C#</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Что такое юнит-тест? Для чего нужен?</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Автопроверка маленького куска логики. Ловит регрессии.
+Что сказать: «Быстрый изолированный тест единицы кода».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E134"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Ответ простыми словами</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="112" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание миграци схемы БД. Какие инструменты вы использовали ?</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Версионирование изменений схемы: EF Migrations, FluentMigrator, SQL-скрипты в CI, в Creatio — через пакеты/схемы объектов.
+Что сказать: «Миграции кодом/скриптами + на Creatio через конфигурацию».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="104" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Ваше понимание принципа ACID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>То же: атомарность, согласованность, изоляция, долговечность.
+Что сказать расшифровку.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="104" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Для чего нужно проводить нормализацию и денормализацию</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Нормализация убирает дубли. Денормализация ускоряет чтение ценой дублирования.
+Что сказать: trade-off целостность vs скорость чтения.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="104" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Если сравнивать аутентификацию Windows и SQL Server, какое из них будет доверенным, а какое – нет?</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Windows auth — доверенная (через ОС/домен). SQL auth — логин/пароль SQL (не «trusted»).
+Что сказать: Windows = trusted, SQL login = нет.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="112" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Есть иерархия классов (A, B: A, C: A). Какую схемы вы бы создали в базе для свойств этих классов?</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Варианты: Table Per Hierarchy / Type / Concrete. Часто одна таблица с типом-дискриминатором или отдельные таблицы + связь.
+Что сказать: «TPH/TPT; выбираю по запросам и простоте».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="104" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Зачем делать SELECT TOP 0</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Получить структуру результата без данных (метаданные/пустой набор) — удобно в ETL/временных таблицах.
+Что сказать: «Схема без строк».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="104" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Как посмотреть список выполняющихся запросов в MSSQL</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>В SQL Server: DMV sys.dm_exec_requests + sys.dm_exec_sql_text / Activity Monitor.
+Что сказать: «DMV / Activity Monitor».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="112" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Как реализовать full join минус inner join.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Строки, которые есть только слева или только справа: FULL OUTER JOIN … WHERE a.key IS NULL OR b.key IS NULL (эмуляция через UNION LEFT/RIGHT тоже возможна).
+Что сказать: «FULL OUTER с фильтром IS NULL с одной из сторон».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="104" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Как реализовать пагинацию в raw sql?</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ORDER BY + OFFSET/FETCH (SQL Server) или LIMIT/OFFSET (PostgreSQL).
+Что сказать: «ORDER BY обязателен + OFFSET/FETCH».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="104" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Какие recovery model существуют, чем отличаются?</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>SQL Server: Simple, Full, Bulk-logged — разный объём лога и возможности point-in-time restore.
+Что сказать три модели и зачем Full для PITR.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="104" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Какие виды операторов вы знаете ?</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>DDL (CREATE), DML (SELECT/INSERT/UPDATE/DELETE), DCL (GRANT), TCL (COMMIT/ROLLBACK).
+Что сказать этот список.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="104" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Какие нормальные формы существуют? Что каждая из них требует?</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>1NF атомарность, 2NF нет частичных зависимостей, 3NF нет транзитивных. Дальше BCNF…
+Что сказать кратко 1–3 NF.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="104" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Какие преимущества и недостатки классов-поставщиков данных, предлагаемых Microsof в ADO.NET?</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>SqlClient и др.: плюс — нативно и быстро под СУБД; минус — привязка к провайдеру, больше кода vs ORM.
+Что сказать: контроль/скорость vs удобство.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Какие соединения поддерживаются Microsoft SQL Server?</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>TCP/IP, Named Pipes, Shared Memory (локально).
+Что сказать эти три.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="104" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Какие СУБД существуют? Виды и конкретные продукты.</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Реляционные: SQL Server, PostgreSQL, Oracle, MySQL. Документные/ключ-значение: Mongo, Redis.
+Что сказать: реляционные + NoSQL примеры.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="104" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Какие типы индексов существуют?</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Кластерный / некластерный, составные, покрывающие, уникальные; в разных СУБД ещё hash/GIN…
+Что сказать: «Как минимум clustered/nonclustered + unique/composite».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Какие типы соединений таблиц существуют?</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>INNER, LEFT, RIGHT, FULL, CROSS.
+Что сказать и кратко объяснить каждый.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="104" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Какова роль класса DataReader в ADO.NET?</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Прямой быстрый forward-only ридер строк из БД в ADO.NET.
+Что сказать: «Потоковое чтение результата SQL».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="104" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Какое значение имеет параметр Initial Catalog в строке соединения?</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Имя базы данных в connection string.
+Что сказать: «К какой БД подключаемся».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="104" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Какой тип столбца вы бы использовали для основного ключа?</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Часто surrogate: IDENTITY/int или uniqueidentifier(Guid). В Creatio — Guid.
+Что сказать: «Стабильный surrogate key; в Creatio Guid».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="104" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Назовите групповой символ в SQL?</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>В LIKE: % (любая длина), _ (один символ). В некоторых СУБД [] и т.п.
+Что сказать: «% и _ в LIKE».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="112" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Нужно реализовать две сущности: сотрудники и должности. У сотрудников должна быть иерархия подчинения. Как?</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Таблица Employee (Id, ManagerId self-FK, PositionId FK) и Position. Иерархия — self-reference ManagerId.
+Что сказать: «Справочник должностей + self-FK руководителя».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="104" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Особенности работы с большим объемом данных</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Индексы, партиции, пагинация, не SELECT *, архивация, batch-обработка, правильная статистика.
+Что сказать этот чеклист.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="104" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Отличие inner join от left join</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>INNER — только совпадения. LEFT — все слева + совпадения справа (иначе NULL).
+Что сказать именно так.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="104" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Расскажите о правиле ACID для транзакций.</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Atomicity Consistency Isolation Durability — всё или ничего, правила целостности, изоляция, сохранность.
+Что сказать расшифровку четырёх букв.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="104" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Сколько таблиц нужно для реализации отношения N:N</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Три: две сущности + таблица связи.
+Что сказать: «Две таблицы + link-таблица».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="116" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Чем TRUNCATE отличается от DELETE.</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>DELETE — строки, можно WHERE, логируется детально.
+TRUNCATE — быстрая очистка всей таблицы, почти без построчного лога.
+Что сказать именно так.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="104" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Что будет, если транзакция останется не закоммиченая?</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Держит блокировки, данные не видны другим (зависит от изоляции), при обрыве — rollback.
+Что сказать: «Долгая незакрытая транзакция = блокировки и риск отката».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование + Собеседование</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="104" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Что такое having</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Фильтр групп после GROUP BY (можно с агрегатами). WHERE — до группировки.
+Что сказать: «WHERE строки, HAVING группы».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="104" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Что такое «уровни изоляции транзакций» и какие бывают</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Read Uncommitted, Read Committed, Repeatable Read, Serializable (+ Snapshot в SQL Server).
+Что сказать список + dirty/non-repeatable/phantom.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="104" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Что такое временная таблица? Как объявить?</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Таблица на время сессии/пакета: #temp в SQL Server или TABLE variable.
+Что сказать: «#temp для промежуточных данных в сессии».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="104" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Что такое курсор?</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Построчный обход результата. Обычно медленнее set-based SQL — используют редко.
+Что сказать: «Построчная обработка; предпочитаю наборные запросы».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собеседование</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Какие бывают виды авторизации при подключении к веб-сервисам</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Basic, bearer(token), куки, В Creatio</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="96" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Какие индексы бывают? Разница и отличие кластеризованных и некластеризованных индекса</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Кластеризованный индекс хранит реальные данные, нельзя создать более одного кластеризованного индекса в таблице.
+Некластеризованный индекс не содержит реальных данных таблицы в узлах-листьях. Узлы-листья содержат один из двух типов информации о местоположении строк данных.</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="200" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Какие способы обеспечения целостности данных предоставляются системами баз данных?</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>1. Обязательное наличие данных. Некоторые столбцы в базе данных должны содержать значения в каждой строке; в таких столбцах не могут содержаться значения NULL или не содержаться никакие значения.данных должны содержать значения в каждой строке;
+2. Условие на значение. У каждого столбца в базе данных есть свой домен, т.е. набор значений, которые допускается хранить в данном. столбце.
+3. Логическая целостность данных. Первичный ключ таблицы должен в каждой строке иметь уникальное значение, отличное от значений во всех
+остальных строках.
+4. Ссылочная целостность. В реляционной базе данных каждая строка дочерней таблицы связана с помощью внешнего ключа со строкой родительской таблицы, содержащей первичный ключ, значение которого равно значению внешнего ключа.
+5. Обновление информации в базе данных может быть ограничено бизнес-правилами, которым. подчиняются сделки, представляемые подобным и обновлениями. Или как способ вернуть сведения о столбце, но не данные на клиентский уровень
+6. Непротиворечивость. Многие реальные деловые операции вызывают в базе данных несколько изменений одновременно. Например, операция
+"прием заказа" может включать в себя добавление строки в таблицу ORDERS, увеличение значения столбца SALES в таблице SALESREPS для
+ел ужащего, принявшего заказ, и увеличение значения столбца SALES в таблице O FF I CES для офиса, за которым закреплен этот служащий. Одна
+инструкция INSERT и две инструкции UPDATE - все они должны быть выполнены для того, чтобы база данных осталась в правильном, непротиворечивом, состоянии. Можно указать СУБД, что следует обеспечивать
+непротиворечивость изменяемых данных.</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Вопросы для собеса + Собес имени меня + Собеседование</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="200" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Представления
+Хранимки
+Триггеры
+Отличия процедур от функций.</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>CREATE VIEW название_представления [(столбец_1, столбец_2, ....)]
+AS выражение_SELECT
+CREATE PROCEDURE [dbo].[sp_InsertUser]
+    @name nvarchar(50),
+    @age int
+AS
+    INSERT INTO Users (Name, Age)
+    VALUES (@name, @age)
+    SELECT SCOPE_IDENTITY()
+GO
+Функция имеет возвращаемый тип и возвращает значение ,не имеет выходных аргументов, вызов хранимой процедуры из функции невозможно, SELECT возможен.
+Хранимая процедура не имеет возвращаемого типа, но имеет выходные аргументы, хранимая процедура имеет и входные, и выходные аргументы, Select не возможен</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="92" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Разница IEnumerable&lt;T&gt; и IQueryable&lt;T&gt; при работе с удаленной БД</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Основное отличие между этими интерфейсами в том, что IEnumerable работает со всем массивом данных, а IQueryable с отфильтрованным. IEnumerable получает все данные на стороне сервера и загружает их в память а затем позволяет сделать фильтрацию по данным из памяти. Когда делается запрос к базе данных, IQueryable выполняет запрос на серверной стороне и в запросе применяет фильтрацию.</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Типы запросов HTTP - POST, GET (чем отличаются) и другие PUT, DELETE, PATCH</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Запрос GET передает данные в URL в виде пар "имя-значение" (другими словами, через ссылку), а запрос POST передает данные в теле запроса.
+Get запросом не стоит отправлять логин пароль - они кешируются, остаются в истории браузера
+GET — метод для чтения данных с сайта.
+HttpPost - это отправка данных на сервер</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="96" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Уровни изоляции транзакций в Sql server</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>READ UNCOMMITTED:
+READ COMMITTED:
+REPEATABLE READ
+SERIALIZABLE</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="144" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>БД</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Что такое нормализация БД. 1, 2, 3 нормальные формы</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Способ убедиться в том, что каждое поле и запись организованы логически таким образом, чтобы не только избежать избыточности, но и сделать использование любой реляционной базы данных более эффективным: избежать ошибок ввода данных, случайного удаления
+1НФ. Согласно правилам, все атрибуты в такой таблице должны быть простыми, все сохраняемые данные на пересечении столбцов и строк — содержать лишь скалярные значения. Также не должно быть повторяющихся строк. 
+2НФ. Отношения будут соответствовать 2НФ, если сама БД находится в 1НФ, а каждый столбец, который не является ключом, зависит от первичного ключа.
+3НФ.</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Ответ простыми словами</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="92" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Document - DOM (объектная модель документа)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Основой HTML-документа являются теги
+Структура документа:
+Первое window document form элементы формы</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="76" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>JS</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>В чём суть Ajax</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>При использовании AJAX нет необходимости обновлять каждый раз всю страницу, так как обновляется только ее конкретная часть. Это намного удобнее, так как не приходится долго ждать, и экономичнее, так как не все обладают безлимитным интернетом.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Ответ простыми словами</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AuthService</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Сервис аутентификации</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>ClientMessageBridge, для чего, как используется, через что передает данные
+Публикация и получение сообщений на клиенте</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>PostMessageToAll, Web socket</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>DataService</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>DataService — серверный API Creatio для работы с данными (CRUD сущностей) извне/интеграций, наряду с OData.
+Что сказать: «Сервис доступа к данным конфигурации Creatio».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="68" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Odata3</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ServiceModel/EntityDataService.svc - предоставляет возможность работы с объектами Creatio в WCF-клиенте.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ProcessEngineService.svc</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Запуск процессов</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="108" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Асинхронность в Entity</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Интерфейс IEntityEventAsyncExecutor — декларирует метод для асинхронного выполнения операций.
+Интерфейс IEntityEventAsyncOperation — декларирует метод для запуска асинхронной операции.
+Класс EntityEventAsyncOperationArgs — экземпляры класса используются в качестве аргумента для передачи в асинхронную операцию.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="112" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Виды аутентификации</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Анонимная аутентификация (Anonymous).
+Базовая аутентификация (Basic-аутентификация).
+Аутентификация на основе cookies (Forms-аутентификация).
+Аутентификация на основе открытого протокола авторизации OAuth 2.0.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Вызов на клиенте</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ProcessModuleUtilities.executeProcess</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="124" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Из каких основных компонентов состоит Creatio, какие компоненты обязательны для его работы</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Обязательно: приложение Creatio (.NET), веб-сервер (IIS), СУБД.
+Часто рядом: Redis (сессии/кэш), файловое хранилище, почта; опционально очереди, поиск.
+Что сказать: «IIS + app + БД; Redis почти всегда на боевых стендах».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="112" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Интеграция Creatio + LDAP AD</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Интеграция с Active Directory/LDAP для пользователей и входа: синхронизация оргструктуры/учёток и SSO-подобная корпоративная аутентификация (настройка в админке Creatio).
+Что сказать: «Синхронизация пользователей/групп из AD + корпоративный вход».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="168" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Использование миксинов</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Миксин — это класс-примесь, предназначенный для расширения функциональности других классов
+define("ИмяМиксина", [], function() {
+   Ext.define("Terrasoft.configuration.mixins.ИмяМиксина", {
+    alternateClassName: "Terrasoft.ИмяМиксина",
+    /* Функциональность миксина. */
+   });
+  return Ext.create(Terrasoft.ИмяМиксина);
+})</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Какие возможности обработки событий измения данных в Creatio</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>EntityEventListener, БП, событийный БП объекта, dependency от колонок на клиенте</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Какие способы работы с БД на клиенте, на бэке.
+Отличия esq и select</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(ESQ, классы Select, Insert, Update и т.д., Entity-model)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="68" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Каким образом можно передать информацию в Creatio</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>OData, конфигурационный сервис, записать напрямую в БД, запустить БП, передав ему параметры с помощью ProcessEngineService</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="176" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Класс ClassFactory</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Реализация фабрики по созданию замещающих объектов Creatio. Фабрика использует open-source фреймворк внедрения зависимостей Ninject. 
+Кейс. Требуется сделать класс хелпер и потом использовать его в сервисе или процессе. То вместо классического 
+var helper = new MyHelper(UserConnection);
+helper.DoMethod();
+Лучше использовать 
+var helper = ClassFactory.Get&lt;MyHelper&gt;(new ConstructorArgument("userConnection", UserConnection));
+helper.DoMethod();</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="84" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Наследование модулей</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Ext.define
+Extend
+AlternateClassName</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="156" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Примеры системных веб-сервисов с аутентификацией на основе cookies
+Примеры системных веб-сервисов с анонимной аутентификацией</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>1. odata — выполнение запросов от внешних приложений к серверу баз данных Creatio по протоколу OData 4. Описание использования протокола OData 4 в Creatio содержится в статье OData.
+2. EntityDataService.svc — выполнение запросов от внешних приложений к серверу баз данных Creatio по протоколу OData 3. Описание использования протокола OData 3 в Creatio содержится в статье OData.
+3. ProcessEngineService.svc — запуск бизнес-процессов Creatio из внешних приложений. Описание веб-сервиса содержится в статье Сервис запуска бизнес-процессов.
+Выполнение запроса на аутентификацию в приложении Creatio.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Протокол Odata 4</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>odata</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="200" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Работа с кешем, уровни хранилища данных
+Когда есть смысл использовать кэширование: 
+Важно понимать, что:</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Session
+Workspace(Данные доступны для всех пользователей одного и того же рабочего пространства),
+Application (Данные доступны всем пользователям приложения вне зависимости от рабочего пространства)
+Пример использования: UserConnection.SessionCache[ключ]
+Часто выполняется выборка одних и тех же данных, которые крайне редко изменяются и это не бизнес-данные в системе (не продажи, клиенты и т.п.)
+Нужно сбрасывать кэш при изменении кэшируемых данных
+Нужно правильно выбирать уровень кэширования (есть кэш уровня приложения, уровня сессии пользователя и уровня конфигурации), _x000B_Кэш уровня сессии удобен тем, что кэш сбрасывается при перелогине в систему. Кэш не будет работать, если данные изменяются в обход приложения</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="156" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Серверный КЭШ</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>При использовании кэширования в серверном коде, суть остается та же, необходимо дополнительно указать параметры кэширования. Но нужно понимать, что при использовании кэширования ESQ кладет результат запроса в именованную ячейку, чтобы брать этот результат, если снова поступит тот же самый запрос, в этом случае ESQ возьмет это самое значение, не будет вычитывать свежие данные из БД. Поэтому важно понимать, что при использовании кэширования нужно предусмотреть механизм сброса кэша, если кэшируемые данные могут измениться при работе в системе. Для этого необходимо выполнять принудительную очистку кэша при добавлении/изменении/удалении кэшируемых данных. Как пример, это можно делать на уровне бизнес процесса объекта и отлавливать сигналы сохранения/удаления и выполнять очистку по данным событиям. Важно так же понимать, что при изменении данных в обход событийной модели приложения, например через БД напрямую, или через классы InsertQuery, UpdateQuery, DeleteQuery – кэш не будет сброшен, будут отлавливаться только события изменения данных через Entity (через приложение).</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Фабрика замещающих классов class ClassFactory</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>var helper = ClassFactory.Get&lt;MyHelper&gt;(new ConstructorArgument("userConnection", UserConnection));
+helper.DoMethod();</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="140" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Фоновое выполнение операций.</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Для запуска фоновых операций в классе Terrasoft.Core.Tasks.Task реализованы методы StartNew() и StartNewWithUserConnection(). В качестве параметров методов можно использовать базовые типы данных в .NET (например, string, int, Guid и т. д.) или пользовательские типы. Отличие метода StartNewWithUserConnection() — запуск фоновой операции, которая требует использования пользовательского соединения UserConnection.
+Параметры, которые принимаются фоновой операцией, преобразуются в массив байт с помощью модуля MessagePack-CSharp. Реализация модуля MessagePack-CSharp содержится на сайте GitHub. Если не удается сериализовать или десериализовать значение параметра, могут сгенерироваться исключения.</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Ответ простыми словами</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Для добавления пользовательского правила поиска дублей необходимо:</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>При необходимости добавить в схему объекта колонку, по значению которой будет выполняться поиск дублей
+Зарегистрировать хранимую процедуру как новое правило поиска дублей
+Добавить хранимую процедуру поиска в базу данных приложения</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="68" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Для чего предназначен компонент «Схемы» в пакетах</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Схемы - элементы конфигурации, которые описывают структуру таблиц базы данных, страниц, бизнес-процессов и исходных кодов конфигурационных классов</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Как вызвать веб-сервис на клиенте?</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>ServiceHelper.callService(“ServiceName”, “Method”, callback, parameters)  scope</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="84" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Как настроить вычисляемое поле на странице редактирования?</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>В коллекцию методов модели представления добавить реализацию метода-обработчика, В модели представления страницы настроить атрибут. В его свойствах указать имена колонок, от которых он зависит, и задать имя обработчика, В атрибуте поля настроить свойство calculateMethodName</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Как получить текст выполняемого SQL-запроса экземпляра класса EntitySchemaQuery?</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>var esqQueryText = esq.GetSelectQuery(UserConnection).GetSqlText()</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Как создать конфигурационный веб-сервис?</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>В схеме «Исходный код» определить класс — наследник класса BaseService. Пометить его атрибутом [ServiceContract]. В классе реализовать методы и типы данных сервиса. Методы пометить атрибутами [OperationContract], типы данных — [DataContract].</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="68" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Какая разница между адресным и широковещательным сообщением?</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>При подписке без канала для адресного сообщения только один подписчик получит передаваемые параметры, Адресное сообщение возвращает объект, а широковещательное — нет</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="92" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Какие из нижеперечисленных задач целесообразно реализовывать с помощью хранимой процедуры в БД?</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Подготовка данных для построения отчетов
+Обработка табличных данных в БД максимально быстрым способом
+Реализация механизма слияния дублей</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="68" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Какие настройки и действия нужно выполнить для перевода локального приложения в режим разработки в файловой системе</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Установить “fileDesignMode enabled ="true", Установить "UseStaticFileContent" value="false", После изменений в Web.config выполнить действие «Компилировать все»,</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Какие функции выполняет атрибут «db» в секции «redis» файла ConnectionStrings.config?</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Указывает на номер базы данных Redis, Должен быть уникальным для каждой среды приложения</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Какие функции выполняет сервер хранения сессий (Redis)?</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Хранение данных сессии пользователей,  Хранение закешированных данных, Обмен данными между узлами web-фермы</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Какими способами можно выполнить загрузку или обновление пакета?</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Использовать утилиту WorkspaceConsole, Выполнить обновление пакета из репозитория системы контроля версий</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Какими способами можно загрузить утилитный модуль на клиент?</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>this.get(“GridData”)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Какой web-сервис необходимо использовать для запуска бизнес-процессов из внешнего приложения?</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>ProcessEngineService.svc</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Какой метод необходимо переопределить для добавления пользовательского действия в раздел (новый пункт меню «Действия»)?</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>getSectionActions</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="104" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>АВ</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Укажите ключевые особенности класса EntitySchemaQuery</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Поддержка прав доступа
+Механизм кэширования
+Возможность построения иерархических запросов
+Возможность постраничного получения данных</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Собес имени меня</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E17"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Вопрос</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Ответ простыми словами</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="104" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Forms-auth - как бы вы реализовали ?</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Логин-форма → cookie аутентификации → модуль проверяет на каждый запрос; роли отдельно.
+Что сказать: «Ticket/cookie после логина».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="104" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mvc Areas - что такое, зачем нужны</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Зоны большого приложения (Admin/Shop) со своими контроллерами/вьюхами.
+Что сказать: «Модульное деление MVC».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="104" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Mvc filters - что такое, зачем нужны, пример</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Атрибуты/фильтры вокруг action: auth, log, exception. Пример Authorize.
+Что сказать: «Cross-cutting до/после action».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="104" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>MVC routing - что это ?</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Сопоставление URL шаблонам → controller/action.
+Что сказать: «Маршрутизация URL на действия».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="104" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Static свойства классов доступны в каждом запросе ?</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Да, static общие на AppDomain/процесс — видны разным запросам. Это опасно для user-данных.
+Что сказать: «Static общий; user-данные туда не класть».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="104" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Дайте пример того, как использование HttpHandler может упростить существующий проект</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Лёгкий обработчик под специальный путь (.ashx) без тяжёлой страницы — отдача файлов, webhook.
+Что сказать: «Точечный endpoint без page lifecycle».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="104" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Динамические контролы на странице - когда инициализировать ?</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Создавать на Init/Load каждый запрос заново с теми же ID, иначе ViewState/события сломаются.
+Что сказать: «Пересоздавать рано и стабильно по ID».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="104" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Жизненый цикл страницы в ASP.NET</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Init → Load → обработчики событий postback → PreRender → Render → Unload (упрощённо).
+Что сказать этапы WebForms lifecycle.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="112" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Используются ли нити (threads) ASP.NET приложения повторно для различных запросов (requests)? Получает ли каждый HttpRequest свою собственную нить? Должны ли вы в ASP.NET использовать Thread Local storage?</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Потоки из пула переиспользуются между запросами. Поэтому нельзя оставлять «грязное» Thread-static/культурное состояние.
+Что сказать: «Пул потоков переиспользуется; контекст запроса изолируйте».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="104" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Как и где можно хранить состояние сессии ?</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>InProc, State Server, SQL Server, Redis/distributive cache. В ферме — не InProc.
+Что сказать: «Для нескольких серверов — out-of-proc (часто Redis)».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="104" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Как можно реализовать наследование в JS?</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Прототипы / class extends / Object.create. В Creatio — Ext.define / extend схем.
+Что сказать: «Прототипное наследование или class sugar».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="104" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Как работают замыкания ?</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Функция помнит внешние переменные lexical scope.
+Что сказать: «Функция + её окружение».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="104" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Какие методы аутентификации есть в IIS?</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Anonymous, Basic, Windows/NTLM/Kerberos, Forms (на уровне app), сертификаты и т.д.
+Что сказать несколько основных.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="104" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Каким образом в приложении можно организовать обмен данных между двумя окнами (window),
+ если одно дочернее и второе родительское ?</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>postMessage, shared localStorage events, BroadcastChannel, cookies (редко).
+Что сказать: «postMessage — безопасный стандарт».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="104" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Каким образом организовать кеширование результата action ?</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>OutputCache / Response Caching / IMemoryCache вокруг результата action с ключом и TTL.
+Что сказать: «Кэш ответа или серверный cache с TTL».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="112" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Каков результат ?
+ function a(x){ x=x+1; var x=10; return x; }; 
+ a(1); a();
+ 10, ибо локально перекрываем глобальный контекст</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Из-за var/подъёма и локальной переменной ответ определяется правилами scope. Готовьтесь объяснить hoisting на примере из билета.
+Что сказать: «Разберу построчно: параметры, var hoist, return».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="104" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Каков результат ?
+ var x = 10; function a(){ console.log(x); var x = 100;} a();
+ undefined, ибо нет ретурна</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Из-за hoisting var x внутри a будет undefined до присваивания — классический вопрос.
+Что сказать: «Hoisting var → undefined до строки присваивания».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="104" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Можно ли сделать роутинг для обработки виртуальных саб-доменов ?</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Да, через route constraints / middleware, читая Host и мапя на параметр tenant.
+Что сказать: «Да, по Host header».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="104" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасности web-приложений</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>HTTPS, валидация входа, параметризация SQL, защита XSS/CSRF, authZ, безопасные cookies, обновления.
+Что сказать этот чеклист.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="104" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Объясните HttpRequest.ValidateInput()</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Проверка входящих данных запроса на потенциально опасный HTML/script (защита от XSS в старых ASP.NET).
+Что сказать: «Валидация входа против XSS».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="112" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Объясните как работают cookies. Дайте пример злоупотребления Cookie.</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Куки — кусочки данных в браузере, уходят с запросами на домен. Злоупотребление: кража сессии, XSS → cookie steal.
+Что сказать: «HttpOnly/Secure; не хранить секреты в обычной куке».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="104" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Что такое Ajax ? Зачем он нужен ?</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Запросы к серверу без полной перезагрузки страницы.
+Что сказать: «Асинхронный обмен данными с сервером в фоне».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="104" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Что такое Membership провайдер ?</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Абстракция ASP.NET для пользователей/паролей (провайдерная модель). Сейчас чаще Identity.
+Что сказать: «Провайдер учёток старого ASP.NET».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="104" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Что такое SessionState и ApplicationState ? Когда какой использовать, можно ли обойтись без них ?</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Session — на пользователя. Application — на всё приложение. Session можно в InProc/StateServer/SQL/Redis.
+Что сказать: Session per user, Application global.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="112" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Что такое viewstate - для чего он нужен, его плюсы и минусы.</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>ViewState в WebForms хранит состояние контролов между постбэками (часто в hidden field). Плюс — удобство; минус — раздувает страницу.
+Что сказать: «Состояние страницы WebForms; тяжёлый трафик».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="104" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Что такое контекст ? Что такое this ?</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>this — текущий контекст вызова функции в JS. В ASP.NET «контекст» часто HttpContext текущего запроса.
+Что сказать: различать JS this и HttpContext.
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="112" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Что такое постбэк ? Можно ли обойтись без него ?</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Postback — повторная отправка страницы на сервер (WebForms). SPA/AJAX могут обойтись без полного постбэка.
+Что сказать: «Полный round-trip страницы; можно заменить AJAX».
+[ответ дополнен]</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Собеседование</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
+++ b/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
@@ -24,7 +24,7 @@
     <sheet name="Ваши_WEB" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C#'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C#'!$A$1:$D$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SQL'!$A$1:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'JavaScript'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Creatio_BPMSoft'!$A$1:$D$16</definedName>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr"/>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="200" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CR</t>
@@ -5756,7 +5756,13 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>(ESQ, классы Select, Insert, Update и т.д., Entity-model)</t>
+          <t>Клиент (JS): в основном ESQ, сервисы (ServiceHelper), иногда OData-подобные вызовы.
+Сервер (C#): Entity, ESQ, Select/Insert/Update/Delete (Core.DB), редко голый SQL.
+Отличие ESQ и Select:
+• ESQ — схемы Creatio + права;
+• Select — SQL-конструктор ближе к БД, гибче, осторожнее с правами.
+Что сказать: «Клиент — ESQ/сервисы; сервер — Entity/ESQ/Core.DB Select».
+[ответ дополнен]</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -7161,7 +7167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7860,10 +7866,53 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>Отличия ESQ и Select (классы Select/Insert/Update)?</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>В Creatio на сервере есть ДВА разных «слоя» работы с данными — их часто путают.
+1) EntitySchemaQuery (ESQ)
+• Работает на уровне СХЕМ объектов Creatio (Contact, Account…).
+• Учитывает права доступа, локализацию, многие правила платформы.
+• Удобен для обычных выборок «по-бизнесовому».
+• Есть и на сервере (C#), и на клиенте (JS).
+• Аналогия: заказать блюдо через официанта ресторана Creatio — он знает меню и правила.
+2) Select / Insert / Update / Delete (Terrasoft.Core.DB)
+• Это конструкторы SQL ближе к «голому» запросу, но через API платформы (не всегда руками пишете текст SQL).
+• Гибче и иногда быстрее для сложных запросов.
+• Права записей сами по себе могут НЕ применяться так, как в ESQ — вы ближе к уровню таблиц БД.
+• Обычно только сервер (C#).
+• Аналогия: пройти на кухню и самому собрать ингредиенты — больше контроля, больше ответственности.
+3) Entity (Fetch/Save)
+• Одна запись: прочитал → поменял поля → Save.
+• Для CRUD одной сущности.
+4) Голый SQL / хранимки
+• Ещё ниже уровнем; только когда без этого никак.
+Когда что:
+• Обычная бизнес-выборка с правами → ESQ.
+• Сложный SQL-образный запрос на сервере, отчёт, тонкая оптимизация → Select/Update…
+• Одна запись → Entity.
+Бонус: у ESQ можно получить SQL-текст:
+esq.GetSelectQuery(UserConnection).GetSqlText()
+— то есть ESQ внутри часто превращается в Select/SQL.
+Что сказать: «ESQ — объектный запрос платформы с правами; Select/Insert/Update — более низкоуровневые SQL-конструкторы Core.DB; Entity — работа с одной записью».</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="220" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Creatio C#</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
           <t>Что такое EntityEventListener?</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Это «сторож» на события записи: перед/после добавления, изменения, удаления.
 Примеры:
@@ -7875,20 +7924,20 @@
 Что сказать: «Подписка на жизненный цикл Entity для валидаций и побочной логики».</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="194" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="194" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Creatio C#</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Процесс Creatio или C#-код — когда что?</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Процесс (визуальный BPM) — когда шаги понятны бизнесу: согласование, письмо, ждать 2 дня, развилка.
 C# — когда сложный алгоритм, интеграция, производительность, много переиспользования.
@@ -7896,20 +7945,20 @@
 Что сказать: «Low-code для оркестрации, код для сложной логики».</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32" ht="208" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="208" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Практика</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Как искать баг «поле иногда не сохраняется»?</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Не гадайте — идите по чеклисту:
 1) Воспроизвести под той же ролью, что у пользователя.
@@ -7920,20 +7969,20 @@
 Что сказать: показать системный подход. Это ценится больше, чем «я сразу знаю причину».</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33" ht="184" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="184" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Делегаты vs интерфейсы</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Когда делегат, когда интерфейс?</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Делегат/Action — одна простая реакция: «когда готово — вызови вот это».
 Интерфейс — набор связанных умений и нормальный объект с жизнью.
@@ -7942,40 +7991,40 @@
 Что сказать: «Делегат для колбэка, интерфейс для зависимости с несколькими операциями».</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34" ht="156" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="156" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Equals</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Зачем Equals и GetHashCode вместе?</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Если кладёте объекты в Dictionary/HashSet как ключи, сравнение и хеш должны быть согласованы: равные объекты → одинаковый hash.
 В CRM обычно равенство записей — по Id (Guid), а не по всем полям.
 Что сказать: «Пара должна быть согласована; для Entity сравниваем по Id».</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35" ht="180" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="180" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Потоки</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Что такое race condition и lock?</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Race — два потока одновременно портят общие данные, как два человека правят один Excel.
 lock — «сейчас работает только один, остальные подождут».
@@ -7983,10 +8032,10 @@
 Что сказать: «Гонка за общее состояние; синхронизация через lock/concurrent-коллекции; static mutable — риск».</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35"/>
+  <autoFilter ref="A1:D36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
+++ b/Creatio_Interview/Собеседование_Creatio_Ответы_Владислав_Пыжьянов.xlsx
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'C#'!$A$1:$D$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SQL'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SQL'!$A$1:$D$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'JavaScript'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Creatio_BPMSoft'!$A$1:$D$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Архитектура_очереди'!$A$1:$D$19</definedName>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5178,18 +5178,15 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>CREATE VIEW название_представления [(столбец_1, столбец_2, ....)]
-AS выражение_SELECT
-CREATE PROCEDURE [dbo].[sp_InsertUser]
-    @name nvarchar(50),
-    @age int
-AS
-    INSERT INTO Users (Name, Age)
-    VALUES (@name, @age)
-    SELECT SCOPE_IDENTITY()
-GO
-Функция имеет возвращаемый тип и возвращает значение ,не имеет выходных аргументов, вызов хранимой процедуры из функции невозможно, SELECT возможен.
-Хранимая процедура не имеет возвращаемого типа, но имеет выходные аргументы, хранимая процедура имеет и входные, и выходные аргументы, Select не возможен</t>
+          <t>VIEW (представление) — сохранённый SELECT «как виртуальная таблица». Обычно данные сам не хранит, при каждом обращении выполняет запрос. Зачем: упростить сложный JOIN, скрыть лишние поля, дать готовую выборку.
+Хранимая процедура («хранимка») — программа внутри БД: параметры, несколько шагов, может читать и менять данные (SELECT/INSERT/UPDATE/DELETE), транзакции. Вызов: EXEC dbo.MyProc @id = 1.
+Триггер — код, который БД запускает автоматически при INSERT/UPDATE/DELETE. Пример: при удалении писать в журнал аудита. Минус: логика скрыта, легко получить рекурсию и тормоза. В Creatio бизнес-логику чаще держат в C#/процессах, не в триггерах.
+Процедура vs функция:
+• Функция должна вернуть значение (число/строку/таблицу) и обычно вызывается из SELECT: SELECT dbo.GetName(@id). В классических функциях SQL Server нельзя свободно менять таблицы.
+• Процедура вызывается через EXEC, может менять данные, иметь OUTPUT-параметры и несколько наборов строк; её нельзя просто подставить в SELECT как скалярную функцию.
+Шпаргалка: VIEW = готовая выборка; процедура = «сделай работу»; функция = «посчитай и верни»; триггер = «сработай сам при изменении».
+Что сказать: именно эту шпаргалку + 1 пример на каждый объект.
+[ответ дополнен]</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -8046,7 +8043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8460,38 +8457,63 @@
       </c>
       <c r="D18" s="5" t="inlineStr"/>
     </row>
-    <row r="19" ht="146" customHeight="1">
+    <row r="19" ht="220" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Объекты БД</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Представления, хранимки, триггеры. Отличия процедур от функций?</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>VIEW (представление) — сохранённый SELECT «как виртуальная таблица». Обычно данные сам не хранит, при каждом обращении выполняет запрос. Зачем: упростить сложный JOIN, скрыть лишние поля, дать готовую выборку.
+Хранимая процедура («хранимка») — программа внутри БД: параметры, несколько шагов, может читать и менять данные (SELECT/INSERT/UPDATE/DELETE), транзакции. Вызов: EXEC dbo.MyProc @id = 1.
+Триггер — код, который БД запускает автоматически при INSERT/UPDATE/DELETE. Пример: при удалении писать в журнал аудита. Минус: логика скрыта, легко получить рекурсию и тормоза. В Creatio бизнес-логику чаще держат в C#/процессах, не в триггерах.
+Процедура vs функция:
+• Функция должна вернуть значение (число/строку/таблицу) и обычно вызывается из SELECT: SELECT dbo.GetName(@id). В классических функциях SQL Server нельзя свободно менять таблицы.
+• Процедура вызывается через EXEC, может менять данные, иметь OUTPUT-параметры и несколько наборов строк; её нельзя просто подставить в SELECT как скалярную функцию.
+Шпаргалка: VIEW = готовая выборка; процедура = «сделай работу»; функция = «посчитай и верни»; триггер = «сработай сам при изменении».
+Что сказать: именно эту шпаргалку + 1 пример на каждый объект.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="146" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>Безопасность</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Что такое SQL injection?</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Злоумышленник вписывает в поле ввода кусок SQL и ломает запрос.
 Защита: никогда не склеивать SQL строкой из текста пользователя. Только параметры.
 Что сказать: «Параметризованные запросы, никаких конкатенаций пользовательского ввода».</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="156" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="156" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>UNION</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>UNION и JOIN — не путать.</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>JOIN — добавить колонки справа (вширь).
 UNION — поставить наборы строк друг под другом (вниз), структура колонок должна совпадать.
@@ -8499,20 +8521,20 @@
 Что сказать: горизонтальная связь vs вертикальное объединение.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="180" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="180" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Creatio SQL</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Особенности БД Creatio для новичка?</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>• Много системных таблиц.
 • Часто soft delete (IsDeleted), а не физическое удаление.
@@ -8521,20 +8543,20 @@
 Что сказать: «Метаданные через конфигурацию; SQL — осознанно; помнить про права и soft delete».</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="174" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="174" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Практика</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Посчитать контакты по каждому аккаунту.</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>SELECT a.Name, COUNT(c.Id) AS Cnt
 FROM Account a
@@ -8544,20 +8566,20 @@
 Условия на контакт лучше в ON, не в WHERE.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="174" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="174" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Практика</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Найти дубли email.</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>SELECT Email, COUNT(*) AS Cnt
 FROM Contact
@@ -8567,29 +8589,29 @@
 Что сказать: GROUP BY + HAVING COUNT(*) &gt; 1 — классика собеса.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="108" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="108" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Практика</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Чем опасен SELECT *?</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Тащите лишние поля, больше сети/памяти, хрупкий код (добавили колонку — всё поехало), сложнее покрывать индексом.
 Что сказать: «Беру только нужные колонки».</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D24"/>
+  <autoFilter ref="A1:D25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
